--- a/resources/templates/standard/L1100-23.xlsx
+++ b/resources/templates/standard/L1100-23.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>설비관리 기준서</t>
   </si>
@@ -680,11 +683,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.15" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -704,45 +709,45 @@
       <c r="T1" s="2"/>
       <c r="U1" s="2"/>
       <c r="V1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W1" s="3"/>
       <c r="X1" s="3"/>
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
       <c r="AA1" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB1" s="3"/>
       <c r="AC1" s="3"/>
       <c r="AD1" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE1" s="3"/>
       <c r="AF1" s="3"/>
       <c r="AG1" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH1" s="3"/>
       <c r="AI1" s="3"/>
       <c r="AJ1" s="3"/>
       <c r="AK1" s="3"/>
       <c r="AL1" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM1" s="4"/>
       <c r="AN1" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO1" s="3"/>
       <c r="AP1" s="3"/>
       <c r="AQ1" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR1" s="3"/>
       <c r="AS1" s="3"/>
       <c r="AT1" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU1" s="3"/>
       <c r="AV1" s="3"/>
@@ -783,7 +788,7 @@
       <c r="AG2" s="5"/>
       <c r="AH2" s="5"/>
       <c r="AI2" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ2" s="6"/>
       <c r="AK2" s="6"/>
@@ -835,7 +840,7 @@
       <c r="AG3" s="8"/>
       <c r="AH3" s="8"/>
       <c r="AI3" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ3" s="7"/>
       <c r="AK3" s="7"/>
@@ -853,7 +858,7 @@
     </row>
     <row r="4" ht="17.15" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -872,11 +877,11 @@
       <c r="P4" s="9"/>
       <c r="Q4" s="9"/>
       <c r="R4" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S4" s="10"/>
       <c r="T4" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
@@ -884,7 +889,7 @@
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
       <c r="Z4" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA4" s="3"/>
       <c r="AB4" s="3"/>
@@ -894,27 +899,27 @@
       <c r="AF4" s="3"/>
       <c r="AG4" s="3"/>
       <c r="AH4" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI4" s="3"/>
       <c r="AJ4" s="3"/>
       <c r="AK4" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL4" s="3"/>
       <c r="AM4" s="3"/>
       <c r="AN4" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO4" s="3"/>
       <c r="AP4" s="3"/>
       <c r="AQ4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR4" s="3"/>
       <c r="AS4" s="3"/>
       <c r="AT4" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU4" s="3"/>
       <c r="AV4" s="3"/>
@@ -959,17 +964,17 @@
       <c r="AI5" s="5"/>
       <c r="AJ5" s="5"/>
       <c r="AK5" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL5" s="13"/>
       <c r="AM5" s="13"/>
       <c r="AN5" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO5" s="5"/>
       <c r="AP5" s="5"/>
       <c r="AQ5" s="14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR5" s="14"/>
       <c r="AS5" s="14"/>
@@ -1475,17 +1480,17 @@
       <c r="AI15" s="16"/>
       <c r="AJ15" s="16"/>
       <c r="AK15" s="17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL15" s="17"/>
       <c r="AM15" s="17"/>
       <c r="AN15" s="17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO15" s="17"/>
       <c r="AP15" s="17"/>
       <c r="AQ15" s="17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR15" s="17"/>
       <c r="AS15" s="17"/>
@@ -1970,22 +1975,22 @@
       <c r="P25" s="11"/>
       <c r="Q25" s="11"/>
       <c r="R25" s="18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S25" s="18"/>
       <c r="T25" s="19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U25" s="19"/>
       <c r="V25" s="19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="W25" s="19"/>
       <c r="X25" s="19"/>
       <c r="Y25" s="19"/>
       <c r="Z25" s="19"/>
       <c r="AA25" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AB25" s="19"/>
       <c r="AC25" s="19"/>
@@ -2000,17 +2005,17 @@
       <c r="AL25" s="19"/>
       <c r="AM25" s="19"/>
       <c r="AN25" s="19" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO25" s="19"/>
       <c r="AP25" s="19"/>
       <c r="AQ25" s="19" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR25" s="19"/>
       <c r="AS25" s="19"/>
       <c r="AT25" s="19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU25" s="19"/>
       <c r="AV25" s="19"/>
